--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92575729244</v>
+        <v>46157.93120759603</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93120759603</v>
+        <v>46157.93186369292</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93186369292</v>
+        <v>46157.93407083247</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93407083247</v>
+        <v>46157.9372521875</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9372521875</v>
+        <v>46158.2822273583</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2822273583</v>
+        <v>46158.29711139479</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29711139479</v>
+        <v>46158.29822783775</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29822783775</v>
+        <v>46158.33393722652</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33393722652</v>
+        <v>46158.36863490043</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36863490043</v>
+        <v>46158.37294476133</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
